--- a/data/trans_dic/P32E$amigos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 52,4</t>
+          <t>12,31; 50,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,6</t>
+          <t>0,0; 47,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 46,11</t>
+          <t>12,98; 47,11</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 45,26</t>
+          <t>9,62; 45,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 57,76</t>
+          <t>16,1; 57,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 44,21</t>
+          <t>17,68; 43,7</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 37,39</t>
+          <t>6,18; 38,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 90,66</t>
+          <t>0,0; 81,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 38,06</t>
+          <t>7,18; 36,84</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 35,41</t>
+          <t>10,72; 36,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 21,26</t>
+          <t>0,85; 20,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 29,39</t>
+          <t>8,94; 28,32</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,21; 33,2</t>
+          <t>15,84; 32,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,36; 36,29</t>
+          <t>9,91; 34,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 30,61</t>
+          <t>16,39; 29,47</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4212; 17892</t>
+          <t>4205; 17289</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5578</t>
+          <t>0; 5146</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6116; 20733</t>
+          <t>5838; 21178</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3487; 14482</t>
+          <t>3079; 14518</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3318; 12474</t>
+          <t>3477; 12517</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9013; 23691</t>
+          <t>9476; 23419</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1545; 8955</t>
+          <t>1480; 9119</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2109; 10924</t>
+          <t>2060; 10576</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6113; 19130</t>
+          <t>5789; 19641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>147; 3731</t>
+          <t>149; 3663</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6797; 21033</t>
+          <t>6398; 20266</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23355; 47840</t>
+          <t>22821; 46973</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6761; 19857</t>
+          <t>5425; 18865</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33115; 60859</t>
+          <t>32587; 58588</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$amigos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 50,63</t>
+          <t>12,72; 55,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,6</t>
+          <t>0,0; 49,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,98; 47,11</t>
+          <t>14,56; 50,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 45,38</t>
+          <t>10,84; 50,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,1; 57,96</t>
+          <t>14,02; 53,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,68; 43,7</t>
+          <t>16,51; 43,54</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 38,08</t>
+          <t>5,52; 34,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,25</t>
+          <t>0,0; 75,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 36,84</t>
+          <t>6,26; 33,73</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,72; 36,36</t>
+          <t>10,49; 37,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 20,87</t>
+          <t>3,41; 47,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 28,32</t>
+          <t>11,14; 33,62</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,84; 32,6</t>
+          <t>16,03; 33,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 34,48</t>
+          <t>12,97; 36,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 29,47</t>
+          <t>17,31; 31,07</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>12433</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4205; 17289</t>
+          <t>4450; 19309</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5146</t>
+          <t>0; 5546</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5838; 21178</t>
+          <t>6707; 23206</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>18620</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3079; 14518</t>
+          <t>4212; 19524</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3477; 12517</t>
+          <t>3531; 13430</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9476; 23419</t>
+          <t>10576; 27886</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5659</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1480; 9119</t>
+          <t>1664; 10419</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 4729</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2060; 10576</t>
+          <t>2277; 12273</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>16217</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5789; 19641</t>
+          <t>6031; 21505</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149; 3663</t>
+          <t>739; 10176</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6398; 20266</t>
+          <t>8819; 26617</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22821; 46973</t>
+          <t>25878; 53549</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5425; 18865</t>
+          <t>8327; 23332</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32587; 58588</t>
+          <t>39074; 70110</t>
         </is>
       </c>
     </row>
